--- a/Class files/Excel-Conditional-Formatting.xlsx
+++ b/Class files/Excel-Conditional-Formatting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel files\Class files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1FEF67-5821-4DBF-9D1D-420FBF583E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780513A9-FC98-49D4-85B2-927DA6DE8B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{25D33E80-4C0C-4E2C-95D8-B675B45B8490}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="16" activeTab="19" xr2:uid="{25D33E80-4C0C-4E2C-95D8-B675B45B8490}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Set" sheetId="2" r:id="rId1"/>
@@ -52,15 +52,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="76">
   <si>
     <t>Excel Conditional Formatting</t>
   </si>
@@ -286,6 +283,9 @@
   <si>
     <t>Darnell Wood</t>
   </si>
+  <si>
+    <t>Status</t>
+  </si>
 </sst>
 </file>
 
@@ -390,7 +390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -465,6 +465,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -472,7 +494,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
@@ -524,6 +546,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{FD7CB597-1BE1-42AA-B259-D337EE2D5649}"/>
@@ -531,7 +560,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{B9B4E8E8-7467-461D-836D-F796786FF1EC}"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="210">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -579,6 +608,222 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -589,6 +834,42 @@
       </fill>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -671,78 +952,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -789,6 +998,16 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color theme="2" tint="-9.9948118533890809E-2"/>
@@ -907,164 +1126,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C5700"/>
       </font>
@@ -1111,6 +1172,370 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color theme="2" tint="-9.9948118533890809E-2"/>
@@ -1211,6 +1636,16 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color theme="2" tint="-9.9948118533890809E-2"/>
@@ -1276,11 +1711,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1321,6 +1756,16 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color theme="2" tint="-9.9948118533890809E-2"/>
@@ -1337,6 +1782,16 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1395,6 +1850,45 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -1402,6 +1896,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color theme="2" tint="-9.9948118533890809E-2"/>
@@ -1436,6 +1940,236 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1484,6 +2218,1045 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C5700"/>
       </font>
@@ -1510,6 +3283,86 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -1561,6 +3414,26 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1571,6 +3444,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color theme="2" tint="-9.9948118533890809E-2"/>
@@ -1607,6 +3490,16 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color theme="2" tint="-9.9948118533890809E-2"/>
@@ -1641,6 +3534,178 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-9.9948118533890809E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -1699,9 +3764,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1739,7 +3804,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1845,7 +3910,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1987,7 +4052,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1996,23 +4061,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44CD2454-AADC-477E-A4BF-2525D0F2A38A}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2021,8 +4086,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
@@ -2038,8 +4103,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2072,7 +4137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -2104,7 +4169,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -2136,7 +4201,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -2168,7 +4233,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -2200,7 +4265,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -2232,7 +4297,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -2264,7 +4329,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -2296,7 +4361,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -2328,45 +4393,45 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M16 A17 C17:M17 A18:M32 B18:F38">
-    <cfRule type="notContainsBlanks" dxfId="72" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="209" priority="3">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="cellIs" dxfId="71" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="208" priority="1" operator="lessThan">
       <formula>3000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="70" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="207" priority="4">
       <formula>LEN(TRIM(H5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2378,23 +4443,23 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F59967-69A1-431D-A06D-909C26822C93}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2403,8 +4468,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>31</v>
       </c>
@@ -2420,8 +4485,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2454,7 +4519,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -2486,7 +4551,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -2518,7 +4583,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -2550,7 +4615,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -2582,7 +4647,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -2614,7 +4679,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -2646,7 +4711,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -2678,7 +4743,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -2710,45 +4775,48 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="45" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="129" priority="4">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="43" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="127" priority="5">
       <formula>LEN(TRIM(B5))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L13">
+    <cfRule type="duplicateValues" dxfId="123" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2757,24 +4825,24 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94E48FC-5AFE-4D00-9C8E-B0A5F4B67416}">
-  <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:N37"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2783,8 +4851,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
@@ -2800,8 +4868,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2834,7 +4902,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44197</v>
       </c>
@@ -2860,13 +4928,13 @@
         <v>8</v>
       </c>
       <c r="K6" s="7">
-        <v>10500</v>
+        <v>13500</v>
       </c>
       <c r="L6" s="8">
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44256</v>
       </c>
@@ -2892,13 +4960,14 @@
         <v>10</v>
       </c>
       <c r="K7" s="7">
-        <v>7500</v>
+        <v>13100</v>
       </c>
       <c r="L7" s="8">
         <v>2150</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N7" s="20"/>
+    </row>
+    <row r="8" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44317</v>
       </c>
@@ -2924,13 +4993,13 @@
         <v>12</v>
       </c>
       <c r="K8" s="7">
-        <v>8900</v>
+        <v>13000</v>
       </c>
       <c r="L8" s="9">
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44378</v>
       </c>
@@ -2956,13 +5025,13 @@
         <v>14</v>
       </c>
       <c r="K9" s="7">
-        <v>8700</v>
+        <v>11400</v>
       </c>
       <c r="L9" s="9">
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44440</v>
       </c>
@@ -2988,13 +5057,13 @@
         <v>16</v>
       </c>
       <c r="K10" s="7">
-        <v>6800</v>
+        <v>10700</v>
       </c>
       <c r="L10" s="8">
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44501</v>
       </c>
@@ -3020,13 +5089,13 @@
         <v>18</v>
       </c>
       <c r="K11" s="7">
-        <v>6100</v>
+        <v>10500</v>
       </c>
       <c r="L11" s="8">
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>44562</v>
       </c>
@@ -3052,13 +5121,13 @@
         <v>20</v>
       </c>
       <c r="K12" s="7">
-        <v>6500</v>
+        <v>10500</v>
       </c>
       <c r="L12" s="9">
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>44621</v>
       </c>
@@ -3084,13 +5153,13 @@
         <v>22</v>
       </c>
       <c r="K13" s="7">
-        <v>7400</v>
+        <v>9700</v>
       </c>
       <c r="L13" s="8">
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>44682</v>
       </c>
@@ -3116,13 +5185,13 @@
         <v>41</v>
       </c>
       <c r="K14" s="7">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="L14" s="7">
         <v>3760</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>44743</v>
       </c>
@@ -3154,7 +5223,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>44805</v>
       </c>
@@ -3180,13 +5249,13 @@
         <v>45</v>
       </c>
       <c r="K16" s="7">
-        <v>10500</v>
+        <v>8800</v>
       </c>
       <c r="L16" s="7">
         <v>4100</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>44866</v>
       </c>
@@ -3212,13 +5281,13 @@
         <v>47</v>
       </c>
       <c r="K17" s="7">
-        <v>9700</v>
+        <v>8700</v>
       </c>
       <c r="L17" s="7">
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>44927</v>
       </c>
@@ -3244,13 +5313,13 @@
         <v>49</v>
       </c>
       <c r="K18" s="7">
-        <v>11400</v>
+        <v>8270</v>
       </c>
       <c r="L18" s="7">
         <v>4700</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>44986</v>
       </c>
@@ -3276,13 +5345,13 @@
         <v>51</v>
       </c>
       <c r="K19" s="7">
-        <v>13100</v>
+        <v>7500</v>
       </c>
       <c r="L19" s="7">
         <v>4300</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>45047</v>
       </c>
@@ -3308,13 +5377,13 @@
         <v>53</v>
       </c>
       <c r="K20" s="7">
-        <v>13000</v>
+        <v>7400</v>
       </c>
       <c r="L20" s="7">
         <v>3600</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>45108</v>
       </c>
@@ -3340,13 +5409,13 @@
         <v>55</v>
       </c>
       <c r="K21" s="7">
-        <v>10700</v>
+        <v>6800</v>
       </c>
       <c r="L21" s="7">
         <v>4300</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>45170</v>
       </c>
@@ -3372,13 +5441,13 @@
         <v>57</v>
       </c>
       <c r="K22" s="7">
-        <v>13500</v>
+        <v>6700</v>
       </c>
       <c r="L22" s="7">
         <v>4200</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>45231</v>
       </c>
@@ -3404,13 +5473,13 @@
         <v>59</v>
       </c>
       <c r="K23" s="7">
-        <v>8270</v>
+        <v>6500</v>
       </c>
       <c r="L23" s="7">
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>45292</v>
       </c>
@@ -3442,7 +5511,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>45352</v>
       </c>
@@ -3468,44 +5537,56 @@
         <v>62</v>
       </c>
       <c r="K25" s="7">
-        <v>6700</v>
+        <v>6100</v>
       </c>
       <c r="L25" s="7">
         <v>3500</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K6:K25">
+    <sortCondition descending="1" ref="K6:K25"/>
+  </sortState>
   <conditionalFormatting sqref="A5:A25 A26:M32">
-    <cfRule type="notContainsBlanks" dxfId="42" priority="8">
+    <cfRule type="notContainsBlanks" dxfId="89" priority="13">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:F38">
-    <cfRule type="notContainsBlanks" dxfId="41" priority="5">
+    <cfRule type="notContainsBlanks" dxfId="88" priority="10">
       <formula>LEN(TRIM(B5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:M25">
-    <cfRule type="notContainsBlanks" dxfId="40" priority="1">
+  <conditionalFormatting sqref="G5:M5 G6:J25 L6:M25">
+    <cfRule type="notContainsBlanks" dxfId="87" priority="6">
       <formula>LEN(TRIM(G5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:K26">
-    <cfRule type="notContainsBlanks" dxfId="39" priority="9">
+    <cfRule type="notContainsBlanks" dxfId="86" priority="14">
       <formula>LEN(TRIM(I26))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O12">
+    <cfRule type="top10" dxfId="85" priority="4" percent="1" rank="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:K25">
+    <cfRule type="aboveAverage" dxfId="84" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L25">
+    <cfRule type="aboveAverage" dxfId="77" priority="1" aboveAverage="0"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3515,23 +5596,23 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E357AD08-8C5F-4440-8DD7-92B91C761DA9}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
-    <col min="4" max="4" width="18.08984375" customWidth="1"/>
-    <col min="5" max="5" width="15.453125" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3540,8 +5621,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>67</v>
       </c>
@@ -3557,8 +5638,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -3591,7 +5672,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44197</v>
       </c>
@@ -3623,7 +5704,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44256</v>
       </c>
@@ -3655,7 +5736,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44317</v>
       </c>
@@ -3687,7 +5768,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44378</v>
       </c>
@@ -3719,7 +5800,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44440</v>
       </c>
@@ -3751,7 +5832,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44501</v>
       </c>
@@ -3783,7 +5864,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>44562</v>
       </c>
@@ -3815,7 +5896,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>44621</v>
       </c>
@@ -3847,7 +5928,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>44682</v>
       </c>
@@ -3879,7 +5960,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>44743</v>
       </c>
@@ -3911,7 +5992,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>44805</v>
       </c>
@@ -3943,7 +6024,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>44866</v>
       </c>
@@ -3975,7 +6056,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>44927</v>
       </c>
@@ -4007,7 +6088,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>44986</v>
       </c>
@@ -4039,7 +6120,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>45047</v>
       </c>
@@ -4071,7 +6152,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>45108</v>
       </c>
@@ -4103,7 +6184,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>45170</v>
       </c>
@@ -4135,7 +6216,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>45231</v>
       </c>
@@ -4167,7 +6248,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>45292</v>
       </c>
@@ -4199,7 +6280,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>45352</v>
       </c>
@@ -4231,31 +6312,34 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="38" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="76" priority="3">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F25">
-    <cfRule type="top10" dxfId="37" priority="1" rank="10"/>
+    <cfRule type="top10" dxfId="75" priority="2" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:L25 I25:K26 B25:F38">
-    <cfRule type="notContainsBlanks" dxfId="36" priority="12">
+    <cfRule type="notContainsBlanks" dxfId="74" priority="13">
       <formula>LEN(TRIM(B25))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L25">
+    <cfRule type="top10" dxfId="70" priority="1" rank="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4265,23 +6349,23 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{899D8220-2D3C-42CD-B17B-6A1B8E634208}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4290,8 +6374,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>66</v>
       </c>
@@ -4307,8 +6391,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -4341,7 +6425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44197</v>
       </c>
@@ -4373,7 +6457,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44256</v>
       </c>
@@ -4405,7 +6489,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44317</v>
       </c>
@@ -4437,7 +6521,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44378</v>
       </c>
@@ -4469,7 +6553,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44440</v>
       </c>
@@ -4501,7 +6585,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44501</v>
       </c>
@@ -4533,7 +6617,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>44562</v>
       </c>
@@ -4565,7 +6649,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>44621</v>
       </c>
@@ -4597,7 +6681,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>44682</v>
       </c>
@@ -4629,7 +6713,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>44743</v>
       </c>
@@ -4661,7 +6745,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>44805</v>
       </c>
@@ -4693,7 +6777,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>44866</v>
       </c>
@@ -4725,7 +6809,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>44927</v>
       </c>
@@ -4757,7 +6841,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>44986</v>
       </c>
@@ -4789,7 +6873,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>45047</v>
       </c>
@@ -4821,7 +6905,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>45108</v>
       </c>
@@ -4853,7 +6937,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>45170</v>
       </c>
@@ -4885,7 +6969,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>45231</v>
       </c>
@@ -4917,7 +7001,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>45292</v>
       </c>
@@ -4949,7 +7033,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>45352</v>
       </c>
@@ -4981,41 +7065,44 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:A25 A26:M32">
-    <cfRule type="notContainsBlanks" dxfId="35" priority="13">
+    <cfRule type="notContainsBlanks" dxfId="69" priority="14">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:F38">
-    <cfRule type="notContainsBlanks" dxfId="34" priority="7">
+    <cfRule type="notContainsBlanks" dxfId="68" priority="8">
       <formula>LEN(TRIM(B5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F25">
-    <cfRule type="top10" dxfId="33" priority="1" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="67" priority="2" percent="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:M25">
-    <cfRule type="notContainsBlanks" dxfId="32" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="66" priority="3">
       <formula>LEN(TRIM(G5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:K26">
-    <cfRule type="notContainsBlanks" dxfId="31" priority="14">
+    <cfRule type="notContainsBlanks" dxfId="65" priority="15">
       <formula>LEN(TRIM(I26))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L25">
+    <cfRule type="top10" dxfId="59" priority="1" percent="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5025,23 +7112,23 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3343C627-248E-4749-B012-5BE72798AB62}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5050,8 +7137,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>33</v>
       </c>
@@ -5067,8 +7154,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5101,7 +7188,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44197</v>
       </c>
@@ -5133,7 +7220,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44256</v>
       </c>
@@ -5165,7 +7252,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44317</v>
       </c>
@@ -5197,7 +7284,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44378</v>
       </c>
@@ -5229,7 +7316,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44440</v>
       </c>
@@ -5261,7 +7348,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44501</v>
       </c>
@@ -5293,7 +7380,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>44562</v>
       </c>
@@ -5325,7 +7412,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>44621</v>
       </c>
@@ -5357,7 +7444,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>44682</v>
       </c>
@@ -5389,7 +7476,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>44743</v>
       </c>
@@ -5421,7 +7508,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>44805</v>
       </c>
@@ -5453,7 +7540,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>44866</v>
       </c>
@@ -5485,7 +7572,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>44927</v>
       </c>
@@ -5517,7 +7604,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>44986</v>
       </c>
@@ -5549,7 +7636,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>45047</v>
       </c>
@@ -5581,7 +7668,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>45108</v>
       </c>
@@ -5613,7 +7700,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>45170</v>
       </c>
@@ -5645,7 +7732,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>45231</v>
       </c>
@@ -5677,7 +7764,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>45292</v>
       </c>
@@ -5709,7 +7796,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>45352</v>
       </c>
@@ -5741,41 +7828,44 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M5 A6:A25 G6:G25 M6:M25 A26:M32">
-    <cfRule type="notContainsBlanks" dxfId="30" priority="9">
+    <cfRule type="notContainsBlanks" dxfId="58" priority="10">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:F38">
-    <cfRule type="notContainsBlanks" dxfId="29" priority="5">
+    <cfRule type="notContainsBlanks" dxfId="57" priority="6">
       <formula>LEN(TRIM(B5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F25">
-    <cfRule type="top10" dxfId="28" priority="1" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="56" priority="2" bottom="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L25">
-    <cfRule type="notContainsBlanks" dxfId="27" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="55" priority="4">
       <formula>LEN(TRIM(H5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:K26">
-    <cfRule type="notContainsBlanks" dxfId="26" priority="10">
+    <cfRule type="notContainsBlanks" dxfId="54" priority="11">
       <formula>LEN(TRIM(I26))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L25">
+    <cfRule type="top10" dxfId="48" priority="1" bottom="1" rank="12"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5785,23 +7875,23 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F13B0C1-06A7-4582-922C-EE92A29AC339}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5810,8 +7900,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>65</v>
       </c>
@@ -5827,8 +7917,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5861,7 +7951,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44197</v>
       </c>
@@ -5893,7 +7983,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44256</v>
       </c>
@@ -5925,7 +8015,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44317</v>
       </c>
@@ -5957,7 +8047,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44378</v>
       </c>
@@ -5989,7 +8079,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44440</v>
       </c>
@@ -6021,7 +8111,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44501</v>
       </c>
@@ -6053,7 +8143,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>44562</v>
       </c>
@@ -6085,7 +8175,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>44621</v>
       </c>
@@ -6117,7 +8207,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>44682</v>
       </c>
@@ -6149,7 +8239,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>44743</v>
       </c>
@@ -6181,7 +8271,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>44805</v>
       </c>
@@ -6213,7 +8303,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>44866</v>
       </c>
@@ -6245,7 +8335,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>44927</v>
       </c>
@@ -6277,7 +8367,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>44986</v>
       </c>
@@ -6309,7 +8399,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>45047</v>
       </c>
@@ -6341,7 +8431,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>45108</v>
       </c>
@@ -6373,7 +8463,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>45170</v>
       </c>
@@ -6405,7 +8495,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>45231</v>
       </c>
@@ -6437,7 +8527,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>45292</v>
       </c>
@@ -6469,7 +8559,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>45352</v>
       </c>
@@ -6501,41 +8591,44 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:A25 A26:M32">
-    <cfRule type="notContainsBlanks" dxfId="25" priority="11">
+    <cfRule type="notContainsBlanks" dxfId="47" priority="12">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:F38">
-    <cfRule type="notContainsBlanks" dxfId="24" priority="6">
+    <cfRule type="notContainsBlanks" dxfId="46" priority="7">
       <formula>LEN(TRIM(B5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F25">
-    <cfRule type="top10" dxfId="23" priority="1" percent="1" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="45" priority="2" percent="1" bottom="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:M25">
-    <cfRule type="notContainsBlanks" dxfId="22" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="44" priority="3">
       <formula>LEN(TRIM(G5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:K26">
-    <cfRule type="notContainsBlanks" dxfId="21" priority="12">
+    <cfRule type="notContainsBlanks" dxfId="43" priority="13">
       <formula>LEN(TRIM(I26))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L25">
+    <cfRule type="top10" dxfId="37" priority="1" percent="1" bottom="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6545,23 +8638,23 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79FAC589-02ED-4FC1-A0D9-08956CDDAE88}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6570,8 +8663,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>64</v>
       </c>
@@ -6587,8 +8680,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -6621,7 +8714,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44197</v>
       </c>
@@ -6653,7 +8746,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44256</v>
       </c>
@@ -6685,7 +8778,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44317</v>
       </c>
@@ -6717,7 +8810,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44378</v>
       </c>
@@ -6749,7 +8842,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44440</v>
       </c>
@@ -6781,7 +8874,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44501</v>
       </c>
@@ -6813,7 +8906,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>44562</v>
       </c>
@@ -6845,7 +8938,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>44621</v>
       </c>
@@ -6877,7 +8970,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>44682</v>
       </c>
@@ -6909,7 +9002,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>44743</v>
       </c>
@@ -6941,7 +9034,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>44805</v>
       </c>
@@ -6973,7 +9066,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>44866</v>
       </c>
@@ -7005,7 +9098,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>44927</v>
       </c>
@@ -7037,7 +9130,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>44986</v>
       </c>
@@ -7069,7 +9162,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>45047</v>
       </c>
@@ -7101,7 +9194,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>45108</v>
       </c>
@@ -7133,7 +9226,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>45170</v>
       </c>
@@ -7165,7 +9258,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>45231</v>
       </c>
@@ -7197,7 +9290,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>45292</v>
       </c>
@@ -7229,7 +9322,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>45352</v>
       </c>
@@ -7261,41 +9354,44 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:A25 A26:M32">
-    <cfRule type="notContainsBlanks" dxfId="20" priority="11">
+    <cfRule type="notContainsBlanks" dxfId="36" priority="12">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:F38">
-    <cfRule type="notContainsBlanks" dxfId="19" priority="6">
+    <cfRule type="notContainsBlanks" dxfId="35" priority="7">
       <formula>LEN(TRIM(B5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F25">
-    <cfRule type="aboveAverage" dxfId="18" priority="1"/>
+    <cfRule type="aboveAverage" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:M25">
-    <cfRule type="notContainsBlanks" dxfId="17" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="33" priority="3">
       <formula>LEN(TRIM(G5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:K26">
-    <cfRule type="notContainsBlanks" dxfId="16" priority="12">
+    <cfRule type="notContainsBlanks" dxfId="32" priority="13">
       <formula>LEN(TRIM(I26))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L25">
+    <cfRule type="aboveAverage" dxfId="26" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7305,23 +9401,23 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6DD1DA-DBD2-46C9-B992-95BA6823D2B1}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7330,8 +9426,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>63</v>
       </c>
@@ -7347,8 +9443,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -7381,7 +9477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44197</v>
       </c>
@@ -7413,7 +9509,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44256</v>
       </c>
@@ -7445,7 +9541,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44317</v>
       </c>
@@ -7477,7 +9573,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44378</v>
       </c>
@@ -7509,7 +9605,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44440</v>
       </c>
@@ -7541,7 +9637,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44501</v>
       </c>
@@ -7573,7 +9669,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>44562</v>
       </c>
@@ -7605,7 +9701,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>44621</v>
       </c>
@@ -7637,7 +9733,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>44682</v>
       </c>
@@ -7669,7 +9765,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>44743</v>
       </c>
@@ -7701,7 +9797,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>44805</v>
       </c>
@@ -7733,7 +9829,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>44866</v>
       </c>
@@ -7765,7 +9861,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>44927</v>
       </c>
@@ -7797,7 +9893,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>44986</v>
       </c>
@@ -7829,7 +9925,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>45047</v>
       </c>
@@ -7861,7 +9957,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>45108</v>
       </c>
@@ -7893,7 +9989,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>45170</v>
       </c>
@@ -7925,7 +10021,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>45231</v>
       </c>
@@ -7957,7 +10053,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>45292</v>
       </c>
@@ -7989,7 +10085,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>45352</v>
       </c>
@@ -8021,41 +10117,44 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:A25 A26:M32">
-    <cfRule type="notContainsBlanks" dxfId="15" priority="11">
+    <cfRule type="notContainsBlanks" dxfId="25" priority="12">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:F38">
-    <cfRule type="notContainsBlanks" dxfId="14" priority="6">
+    <cfRule type="notContainsBlanks" dxfId="24" priority="7">
       <formula>LEN(TRIM(B5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F25">
-    <cfRule type="aboveAverage" dxfId="13" priority="1" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="23" priority="2" aboveAverage="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:M25">
-    <cfRule type="notContainsBlanks" dxfId="12" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="22" priority="3">
       <formula>LEN(TRIM(G5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:K26">
-    <cfRule type="notContainsBlanks" dxfId="11" priority="12">
+    <cfRule type="notContainsBlanks" dxfId="21" priority="13">
       <formula>LEN(TRIM(I26))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L25">
+    <cfRule type="aboveAverage" dxfId="15" priority="1" aboveAverage="0"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8065,23 +10164,23 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E2A2BD-75B0-4E9D-9E2C-7D11A9953D82}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8090,8 +10189,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>38</v>
       </c>
@@ -8107,8 +10206,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -8141,7 +10240,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -8173,7 +10272,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -8205,7 +10304,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -8237,7 +10336,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -8269,7 +10368,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -8301,7 +10400,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -8333,7 +10432,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -8365,7 +10464,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -8397,40 +10496,40 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="10" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="14" priority="4">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -8444,8 +10543,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="9" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="13" priority="5">
       <formula>LEN(TRIM(B5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L13">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1DF447B1-3559-4354-BC55-1A77E9463698}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8466,6 +10579,19 @@
           </x14:cfRule>
           <xm:sqref>F6:F13</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1DF447B1-3559-4354-BC55-1A77E9463698}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L6:L13</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -8475,23 +10601,23 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9ECAA4-9358-4D82-A6C6-4D4E4792523C}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8500,8 +10626,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
@@ -8517,8 +10643,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -8551,7 +10677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -8583,7 +10709,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -8615,7 +10741,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -8647,7 +10773,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -8679,7 +10805,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -8711,7 +10837,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -8743,7 +10869,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -8775,7 +10901,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -8807,40 +10933,40 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="8" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="10" priority="4">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8852,8 +10978,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="7" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="9" priority="5">
       <formula>LEN(TRIM(B5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L13">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8864,23 +11002,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EBBBD5-7783-4481-B052-EE814583B9B8}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="15.54296875" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8889,8 +11027,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
@@ -8906,8 +11044,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -8940,7 +11078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -8972,7 +11110,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -9004,7 +11142,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -9036,7 +11174,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -9068,7 +11206,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -9100,7 +11238,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -9132,7 +11270,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -9164,7 +11302,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -9196,41 +11334,51 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M19 A20:F20 H20:M20 A21:M31 A32 C32:M32 B33:F38">
-    <cfRule type="notContainsBlanks" dxfId="69" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="201" priority="3">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="68" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="200" priority="4">
       <formula>LEN(TRIM(H5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E13">
+    <cfRule type="cellIs" dxfId="199" priority="2" operator="equal">
+      <formula>10500</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="cellIs" dxfId="195" priority="1" operator="equal">
+      <formula>$D$8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9240,24 +11388,24 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0ADF68-0BC8-492D-80D8-CCF770A44C21}">
-  <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:M37"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9266,8 +11414,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>35</v>
       </c>
@@ -9283,8 +11431,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -9316,8 +11464,11 @@
       <c r="L5" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M5" s="21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -9348,8 +11499,12 @@
       <c r="L6" s="8">
         <v>5000</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M6" t="str">
+        <f>IF(L6&gt;=4000,"😀",IF(L6&gt;=2500,"😐","☹️"))</f>
+        <v>😀</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -9380,8 +11535,12 @@
       <c r="L7" s="8">
         <v>2150</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M7" t="str">
+        <f t="shared" ref="M7:M13" si="0">IF(L7&gt;=4000,"😀",IF(L7&gt;=2500,"😐","☹️"))</f>
+        <v>☹️</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -9412,8 +11571,12 @@
       <c r="L8" s="9">
         <v>4510</v>
       </c>
-    </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M8" t="str">
+        <f t="shared" si="0"/>
+        <v>😀</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -9444,8 +11607,12 @@
       <c r="L9" s="9">
         <v>3150</v>
       </c>
-    </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M9" t="str">
+        <f t="shared" si="0"/>
+        <v>😐</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -9476,8 +11643,12 @@
       <c r="L10" s="8">
         <v>2100</v>
       </c>
-    </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M10" t="str">
+        <f t="shared" si="0"/>
+        <v>☹️</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -9508,8 +11679,12 @@
       <c r="L11" s="8">
         <v>2175</v>
       </c>
-    </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M11" t="str">
+        <f t="shared" si="0"/>
+        <v>☹️</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -9540,8 +11715,12 @@
       <c r="L12" s="9">
         <v>2255</v>
       </c>
-    </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M12" t="str">
+        <f t="shared" si="0"/>
+        <v>☹️</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -9572,42 +11751,55 @@
       <c r="L13" s="8">
         <v>3150</v>
       </c>
-    </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M13" t="str">
+        <f t="shared" si="0"/>
+        <v>😐</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="6" priority="3">
+  <conditionalFormatting sqref="A5:M5 A14:M32 A6:L13">
+    <cfRule type="notContainsBlanks" dxfId="6" priority="4">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="5" priority="5">
       <formula>LEN(TRIM(B5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L13">
+    <cfRule type="iconSet" priority="1">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9616,7 +11808,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{FF4FD276-2C41-43D7-AE80-92A80D421020}">
+          <x14:cfRule type="iconSet" priority="2" id="{FF4FD276-2C41-43D7-AE80-92A80D421020}">
             <x14:iconSet iconSet="3Triangles">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -9640,23 +11832,23 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{683DFA13-DE5C-43AA-A0EE-602EA068AC65}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="13.6328125" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9665,8 +11857,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>36</v>
       </c>
@@ -9682,8 +11874,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
         <v>2</v>
       </c>
@@ -9716,7 +11908,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="14">
         <v>44641</v>
       </c>
@@ -9748,7 +11940,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="14">
         <v>44708</v>
       </c>
@@ -9780,7 +11972,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="14">
         <v>44775</v>
       </c>
@@ -9812,7 +12004,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="14">
         <v>44842</v>
       </c>
@@ -9844,7 +12036,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="14">
         <v>44909</v>
       </c>
@@ -9876,7 +12068,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="14">
         <v>44976</v>
       </c>
@@ -9908,7 +12100,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="14">
         <v>45043</v>
       </c>
@@ -9940,7 +12132,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="14">
         <v>45110</v>
       </c>
@@ -9972,40 +12164,40 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="206" priority="2" operator="greaterThan">
       <formula>3550</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L13">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="205" priority="1" operator="greaterThan">
       <formula>3550</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10017,23 +12209,23 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684CDAFD-40BE-4F05-875F-2118E3275E36}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="13.6328125" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10042,8 +12234,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>37</v>
       </c>
@@ -10059,8 +12251,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -10093,7 +12285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -10125,7 +12317,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -10157,7 +12349,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -10189,7 +12381,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -10221,7 +12413,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -10253,7 +12445,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -10285,7 +12477,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -10317,7 +12509,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -10349,48 +12541,33 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="3">
-      <formula>LEN(TRIM(A5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="4">
-      <formula>LEN(TRIM(B5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L13">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>3000</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -10399,23 +12576,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7302F484-0D1A-42B9-91BF-7161D00A2278}">
   <dimension ref="B1:M37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10424,8 +12601,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:13" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
@@ -10441,8 +12618,8 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -10475,7 +12652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -10507,7 +12684,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -10539,7 +12716,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -10571,7 +12748,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -10603,7 +12780,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -10635,7 +12812,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -10667,7 +12844,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -10699,7 +12876,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -10731,46 +12908,51 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:G29 I5:M29 A30:M32">
-    <cfRule type="notContainsBlanks" dxfId="67" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="194" priority="4">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:F38 J14:L26">
-    <cfRule type="notContainsBlanks" dxfId="66" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="193" priority="5">
       <formula>LEN(TRIM(B5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="192" priority="2" operator="greaterThan">
       <formula>4000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M6:M13">
+    <cfRule type="cellIs" dxfId="188" priority="1" operator="greaterThan">
+      <formula>3500</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10781,23 +12963,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57D7FDC-53F8-4A50-8D90-8CC1687235F5}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10806,8 +12988,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
@@ -10823,8 +13005,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -10857,7 +13039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -10889,7 +13071,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -10921,7 +13103,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -10953,7 +13135,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -10985,7 +13167,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -11017,7 +13199,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -11049,7 +13231,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -11081,7 +13263,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -11113,46 +13295,66 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="19">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="19">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="64" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="144" priority="5">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="187" priority="3" operator="greaterThan">
       <formula>3550</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="62" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="143" priority="6">
       <formula>LEN(TRIM(B5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6">
+    <cfRule type="cellIs" dxfId="186" priority="2" operator="between">
+      <formula>2000</formula>
+      <formula>4000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L13">
+    <cfRule type="cellIs" dxfId="142" priority="1" operator="between">
+      <formula>2000</formula>
+      <formula>3000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11163,23 +13365,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F776A9A-3AF5-4A41-9FDF-9E00F985DE0E}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11188,8 +13390,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>26</v>
       </c>
@@ -11205,8 +13407,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -11239,7 +13441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -11271,7 +13473,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -11303,7 +13505,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -11335,7 +13537,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -11367,7 +13569,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -11399,7 +13601,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -11431,7 +13633,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -11463,7 +13665,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -11495,46 +13697,51 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="61" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="180" priority="4">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="cellIs" dxfId="60" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="179" priority="2" operator="lessThan">
       <formula>2500</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="59" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="178" priority="5">
       <formula>LEN(TRIM(B5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L13">
+    <cfRule type="cellIs" dxfId="174" priority="1" operator="lessThan">
+      <formula>3500</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11545,23 +13752,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2972C7E-6E83-4748-85DD-CB06EEF3570A}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11570,8 +13777,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>27</v>
       </c>
@@ -11587,8 +13794,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -11621,7 +13828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -11653,7 +13860,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -11685,7 +13892,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -11717,7 +13924,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -11749,7 +13956,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -11781,7 +13988,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -11813,7 +14020,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -11845,7 +14052,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -11877,47 +14084,53 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="58" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="173" priority="4">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="cellIs" dxfId="57" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="172" priority="2" operator="between">
       <formula>2500</formula>
       <formula>4000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="56" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="171" priority="5">
       <formula>LEN(TRIM(B5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L13">
+    <cfRule type="cellIs" dxfId="167" priority="1" operator="between">
+      <formula>2000</formula>
+      <formula>3000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11928,23 +14141,23 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B85CB176-ABCB-46E9-8CF3-F60FE40338AF}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11953,8 +14166,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
@@ -11970,8 +14183,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -12004,7 +14217,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>44641</v>
       </c>
@@ -12036,7 +14249,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>44708</v>
       </c>
@@ -12068,7 +14281,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>44775</v>
       </c>
@@ -12100,7 +14313,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>44842</v>
       </c>
@@ -12132,7 +14345,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>44909</v>
       </c>
@@ -12164,7 +14377,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>44976</v>
       </c>
@@ -12196,7 +14409,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45043</v>
       </c>
@@ -12228,7 +14441,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45110</v>
       </c>
@@ -12260,46 +14473,51 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="55" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="166" priority="4">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="2" operator="equal">
       <formula>2100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
-    <cfRule type="notContainsBlanks" dxfId="53" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="164" priority="5">
       <formula>LEN(TRIM(B5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L13">
+    <cfRule type="cellIs" dxfId="160" priority="1" operator="equal">
+      <formula>5000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12310,23 +14528,23 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B19B2F-7AC0-4B20-9DA9-EFC99F1D029F}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12335,8 +14553,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>29</v>
       </c>
@@ -12352,8 +14570,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>39</v>
       </c>
@@ -12386,7 +14604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>68</v>
       </c>
@@ -12418,7 +14636,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>72</v>
       </c>
@@ -12450,7 +14668,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
         <v>69</v>
       </c>
@@ -12482,7 +14700,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>68</v>
       </c>
@@ -12514,7 +14732,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>70</v>
       </c>
@@ -12546,7 +14764,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>71</v>
       </c>
@@ -12569,7 +14787,7 @@
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K11" s="7">
         <v>6100</v>
@@ -12578,7 +14796,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5" t="s">
         <v>72</v>
       </c>
@@ -12610,7 +14828,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>69</v>
       </c>
@@ -12642,51 +14860,61 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="52" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="155" priority="6">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B13">
-    <cfRule type="containsText" dxfId="51" priority="1" operator="containsText" text="Printer">
+    <cfRule type="containsText" dxfId="154" priority="3" operator="containsText" text="Printer">
       <formula>NOT(ISERROR(SEARCH("Printer",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:F13">
-    <cfRule type="containsText" dxfId="50" priority="7" operator="containsText" text="Paper">
+    <cfRule type="containsText" dxfId="153" priority="9" operator="containsText" text="Paper">
       <formula>NOT(ISERROR(SEARCH("Paper",C6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:L13 I14:K26 B14:F38">
-    <cfRule type="notContainsBlanks" dxfId="49" priority="10">
+    <cfRule type="notContainsBlanks" dxfId="152" priority="12">
       <formula>LEN(TRIM(B5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="151" priority="2" operator="equal">
+      <formula>$J$7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:J13">
+    <cfRule type="cellIs" dxfId="145" priority="1" operator="equal">
+      <formula>$J$7</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12697,23 +14925,23 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2571A97A-A376-4A9B-86F9-18C82FBEB609}">
   <dimension ref="B1:L37"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12722,8 +14950,8 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>30</v>
       </c>
@@ -12739,8 +14967,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -12773,7 +15001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>45047</v>
       </c>
@@ -12805,7 +15033,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>45078</v>
       </c>
@@ -12837,7 +15065,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>45108</v>
       </c>
@@ -12869,7 +15097,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>45139</v>
       </c>
@@ -12901,7 +15129,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>45170</v>
       </c>
@@ -12933,7 +15161,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>45200</v>
       </c>
@@ -12965,7 +15193,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>45231</v>
       </c>
@@ -12997,7 +15225,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>45261</v>
       </c>
@@ -13029,46 +15257,54 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <conditionalFormatting sqref="H5:L13 I14:K26 B5:F38">
-    <cfRule type="notContainsBlanks" dxfId="48" priority="4">
-      <formula>LEN(TRIM(B5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A5:M32">
-    <cfRule type="notContainsBlanks" dxfId="47" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="138" priority="5">
       <formula>LEN(TRIM(A5))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B13">
-    <cfRule type="timePeriod" dxfId="46" priority="1" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="137" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(B6)=MONTH(EDATE(TODAY(),0-1)),YEAR(B6)=YEAR(EDATE(TODAY(),0-1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:L13 B5:F38 I14:K26">
+    <cfRule type="notContainsBlanks" dxfId="136" priority="6">
+      <formula>LEN(TRIM(B5))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6:H13">
+    <cfRule type="cellIs" dxfId="130" priority="2" operator="equal">
+      <formula>44866</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="131" priority="1" operator="equal">
+      <formula>$H$8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
